--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -2038,17 +2038,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NK Istra 1961</t>
+          <t>IFK Värnamo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2068,7 +2068,7 @@
         <v>2004</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>46934</v>
+        <v>47118</v>
       </c>
       <c r="J37" t="n">
         <v>265000</v>
@@ -2604,13 +2604,25 @@
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>2006</v>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="I50" s="1" t="n">
+        <v>46568</v>
+      </c>
+      <c r="J50" t="n">
+        <v>210000</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5231,12 +5243,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NK Maribor</t>
+          <t>Ilirija 1911</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PrvaLiga</t>
+          <t>2nd SNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6039,12 +6051,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Kety Emmi Bistrica</t>
+          <t>Rudar Velenje</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Slovenia Cup</t>
+          <t>2nd SNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6068,7 +6080,9 @@
       <c r="H128" t="n">
         <v>2003</v>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" s="1" t="n">
+        <v>46203</v>
+      </c>
       <c r="J128" t="n">
         <v>110000</v>
       </c>
@@ -6465,12 +6479,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FK Vojvodina</t>
+          <t>FK Kabel Novi Sad</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mozzart Bet Superliga</t>
+          <t>Mozzart Bet Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6512,7 +6526,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>BSC Young Boys</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7199,17 +7213,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BK Häcken U19</t>
+          <t>BK Häcken</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>U19 Allsvenskan, Sodra</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Sweden Amateur</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7539,17 +7553,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Queens Park Rangers U21</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Professional Development League</t>
+          <t>Championship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>England Amateur</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8381,12 +8395,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>IFK Värnamo</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Superettan</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -12267,7 +12281,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Kuopion Palloseura</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -14317,7 +14331,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>FC Viktoria Plzeň</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -15451,7 +15465,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Urartu</t>
+          <t>BKMA Yerevan</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -15884,7 +15898,7 @@
         </is>
       </c>
       <c r="F348" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
@@ -17920,19 +17934,11 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PFK Montana 1921</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>Vtora Liga</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
+          <t>No team</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr">
         <is>
           <t>Bulgaria</t>
@@ -17949,9 +17955,7 @@
       <c r="H397" t="n">
         <v>2005</v>
       </c>
-      <c r="I397" s="1" t="n">
-        <v>46203</v>
-      </c>
+      <c r="I397" t="inlineStr"/>
       <c r="J397" t="n">
         <v>97000</v>
       </c>
@@ -18783,17 +18787,17 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>FC Sellier &amp;amp; Bellot Vlašim</t>
+          <t>FC Dila Gori</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>FNL</t>
+          <t>Erovnuli Liga</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -20285,12 +20289,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KAA Gent Reserve U23</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Pro League</t>
+          <t>U21 Pro League</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -21689,7 +21693,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>FC Viktoria Plzeň</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -21779,12 +21783,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>NK Maribor</t>
+          <t>Ilirija 1911</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>PrvaLiga</t>
+          <t>2nd SNL</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -24106,7 +24110,11 @@
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
-      <c r="G536" t="inlineStr"/>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H536" t="n">
         <v>2007</v>
       </c>

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K482"/>
+  <dimension ref="A1:K492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,7 +653,9 @@
       <c r="H5" t="n">
         <v>2004</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" s="1" t="n">
+        <v>46568</v>
+      </c>
       <c r="J5" t="n">
         <v>145000</v>
       </c>
@@ -4601,12 +4603,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FK Kabel Novi Sad</t>
+          <t>FK Vojvodina</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mozzart Bet Prva Liga</t>
+          <t>Mozzart Bet Superliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5219,7 +5221,9 @@
       <c r="H107" t="n">
         <v>2007</v>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" s="1" t="n">
+        <v>47118</v>
+      </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
     </row>
@@ -5501,17 +5505,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Queens Park Rangers U21</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Championship</t>
+          <t>Professional Development League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>England Amateur</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6289,7 +6293,7 @@
         <v>2004</v>
       </c>
       <c r="I132" s="1" t="n">
-        <v>46568</v>
+        <v>46356</v>
       </c>
       <c r="J132" t="n">
         <v>390000</v>
@@ -11966,7 +11970,11 @@
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H256" t="n">
         <v>2006</v>
       </c>
@@ -12270,8 +12278,14 @@
           <t>Estonia</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
+      <c r="F263" t="n">
+        <v>188</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H263" t="n">
         <v>2009</v>
       </c>
@@ -12340,24 +12354,40 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool U21</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr"/>
+          <t>Harju Jalgpallikool</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Cup</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>Estonia</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
+      <c r="F265" t="n">
+        <v>189</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H265" t="n">
         <v>2004</v>
       </c>
-      <c r="I265" t="inlineStr"/>
+      <c r="I265" s="1" t="n">
+        <v>46752</v>
+      </c>
       <c r="J265" t="n">
-        <v>26000</v>
+        <v>260000</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
@@ -13544,7 +13574,9 @@
           <t>Estonia</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr"/>
+      <c r="F293" t="n">
+        <v>182</v>
+      </c>
       <c r="G293" t="inlineStr">
         <is>
           <t>Right</t>
@@ -13554,7 +13586,7 @@
         <v>2007</v>
       </c>
       <c r="I293" s="1" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr"/>
@@ -13642,7 +13674,7 @@
         <v>2008</v>
       </c>
       <c r="I295" s="1" t="n">
-        <v>46387</v>
+        <v>47118</v>
       </c>
       <c r="J295" t="n">
         <v>27000</v>
@@ -15361,7 +15393,7 @@
         <v>2008</v>
       </c>
       <c r="I336" s="1" t="n">
-        <v>46568</v>
+        <v>47664</v>
       </c>
       <c r="J336" t="n">
         <v>47000</v>
@@ -15963,19 +15995,11 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>FC Dila Gori</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>Erovnuli Liga</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>Georgia</t>
-        </is>
-      </c>
+          <t>No team</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
           <t>Angola</t>
@@ -18099,12 +18123,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Young Violets Austria Wien</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2. Liga</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -18473,7 +18497,9 @@
           <t>Romania</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr"/>
+      <c r="F406" t="n">
+        <v>178</v>
+      </c>
       <c r="G406" t="inlineStr">
         <is>
           <t>Right</t>
@@ -18987,7 +19013,7 @@
         <v>2006</v>
       </c>
       <c r="I418" s="1" t="n">
-        <v>46904</v>
+        <v>46387</v>
       </c>
       <c r="J418" t="n">
         <v>290000</v>
@@ -20264,7 +20290,9 @@
       <c r="H446" t="n">
         <v>2006</v>
       </c>
-      <c r="I446" t="inlineStr"/>
+      <c r="I446" s="1" t="n">
+        <v>46203</v>
+      </c>
       <c r="J446" t="n">
         <v>330000</v>
       </c>
@@ -21183,7 +21211,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>ACS FC Corvinul Hunedoara</t>
+          <t>FC Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -21619,12 +21647,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>MŠK Žilina U19</t>
+          <t>MŠK Žilina</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>U19 1. Liga</t>
+          <t>Niké Liga</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -21637,7 +21665,9 @@
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="F478" t="inlineStr"/>
+      <c r="F478" t="n">
+        <v>182</v>
+      </c>
       <c r="G478" t="inlineStr"/>
       <c r="H478" t="n">
         <v>2008</v>
@@ -21837,6 +21867,470 @@
         <v>47000</v>
       </c>
       <c r="K482" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>635</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>FC Liefering</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2. Liga</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="F483" t="n">
+        <v>194</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H483" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I483" s="1" t="n">
+        <v>47299</v>
+      </c>
+      <c r="J483" t="n">
+        <v>325000</v>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>636</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Rosenborg BK</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Eliteserien</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="F484" t="n">
+        <v>195</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H484" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I484" s="1" t="n">
+        <v>47483</v>
+      </c>
+      <c r="J484" t="n">
+        <v>925000</v>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>637</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Miedź Legnica</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>I liga</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="F485" t="n">
+        <v>180</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H485" t="n">
+        <v>2006</v>
+      </c>
+      <c r="I485" s="1" t="n">
+        <v>46934</v>
+      </c>
+      <c r="J485" t="n">
+        <v>260000</v>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>638</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Miedź Legnica</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>I liga</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="F486" t="n">
+        <v>180</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H486" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I486" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="J486" t="n">
+        <v>380000</v>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>639</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>RFS</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Virsliga</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="F487" t="n">
+        <v>170</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="H487" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I487" s="1" t="n">
+        <v>47118</v>
+      </c>
+      <c r="J487" t="n">
+        <v>140000</v>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>640</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>FC Liefering</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2. Liga</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="F488" t="n">
+        <v>186</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H488" t="n">
+        <v>2006</v>
+      </c>
+      <c r="I488" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="J488" t="n">
+        <v>325000</v>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>641</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>SC Austria Lustenau</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2. Liga</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Mali</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H489" t="n">
+        <v>2004</v>
+      </c>
+      <c r="I489" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="J489" t="n">
+        <v>195000</v>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>642</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>NK Olimpija Ljubljana</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>PrvaLiga</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="F490" t="n">
+        <v>187</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H490" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I490" s="1" t="n">
+        <v>47269</v>
+      </c>
+      <c r="J490" t="n">
+        <v>620000</v>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>643</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Västerås SK</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Superettan</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="F491" t="n">
+        <v>184</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H491" t="n">
+        <v>2004</v>
+      </c>
+      <c r="I491" s="1" t="n">
+        <v>47118</v>
+      </c>
+      <c r="J491" t="n">
+        <v>600000</v>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>644</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Polonia Bytom</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>III Liga, Group 3</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="F492" t="n">
+        <v>178</v>
+      </c>
+      <c r="G492" t="inlineStr"/>
+      <c r="H492" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I492" s="1" t="n">
+        <v>46934</v>
+      </c>
+      <c r="J492" t="n">
+        <v>360000</v>
+      </c>
+      <c r="K492" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -1088,7 +1088,9 @@
       <c r="H14" t="n">
         <v>2005</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" s="2" t="n">
+        <v>46568</v>
+      </c>
       <c r="J14" t="n">
         <v>580000</v>
       </c>
@@ -1378,12 +1380,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb U19</t>
+          <t>NK Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prva NL Juniori</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2082,12 +2084,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jong VVV-Venlo</t>
+          <t>VVV-Venlo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Reservecompetitie, 2nd Stage, Group A</t>
+          <t>Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2115,12 +2117,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jong VVV-Venlo</t>
+          <t>VVV-Venlo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Reservecompetitie, 2nd Stage, Group A</t>
+          <t>Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3009,7 +3011,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kristiansund BK</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3535,7 +3537,7 @@
         <v>47299</v>
       </c>
       <c r="J69" t="n">
-        <v>1100000</v>
+        <v>1600000</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -4697,9 +4699,7 @@
       <c r="H95" t="n">
         <v>2005</v>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>47664</v>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
         <v>5300000</v>
       </c>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Djurgårdens IF</t>
+          <t>Nordic United FC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Division 2, Sodra Svealand</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5802,7 +5802,7 @@
         <v>46752</v>
       </c>
       <c r="J120" t="n">
-        <v>580000</v>
+        <v>630000</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -6244,12 +6244,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IK Sirius</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ettan, Norra</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>GY-M-S Megye I. osztály</t>
+          <t>Gy-M-S Vármegyei I. osztály</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7526,9 +7526,11 @@
       <c r="H158" t="n">
         <v>2004</v>
       </c>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" s="2" t="n">
+        <v>46934</v>
+      </c>
       <c r="J158" t="n">
-        <v>670000</v>
+        <v>480000</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -7667,7 +7669,7 @@
         <v>47299</v>
       </c>
       <c r="J161" t="n">
-        <v>415000</v>
+        <v>740000</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -7759,7 +7761,7 @@
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="n">
-        <v>775000</v>
+        <v>970000</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -7894,9 +7896,7 @@
       <c r="H166" t="n">
         <v>2005</v>
       </c>
-      <c r="I166" s="2" t="n">
-        <v>47483</v>
-      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="J166" t="n">
         <v>1100000</v>
       </c>
@@ -8497,9 +8497,7 @@
       <c r="H179" t="n">
         <v>2004</v>
       </c>
-      <c r="I179" s="2" t="n">
-        <v>47299</v>
-      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="J179" t="n">
         <v>1300000</v>
       </c>
@@ -9122,17 +9120,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>FK Pardubice</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Czech First League</t>
+          <t>Veikkausliiga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -9149,7 +9147,9 @@
       <c r="H193" t="n">
         <v>2005</v>
       </c>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" s="2" t="n">
+        <v>46387</v>
+      </c>
       <c r="J193" t="n">
         <v>140000</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>47118</v>
       </c>
       <c r="J197" t="n">
-        <v>385000</v>
+        <v>410000</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>48029</v>
       </c>
       <c r="J200" t="n">
-        <v>1300000</v>
+        <v>5400000</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -9570,7 +9570,7 @@
         <v>46568</v>
       </c>
       <c r="J202" t="n">
-        <v>420000</v>
+        <v>470000</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -10158,7 +10158,9 @@
           <t>Finland</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
+      <c r="F215" t="n">
+        <v>170</v>
+      </c>
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="n">
         <v>2008</v>
@@ -10251,9 +10253,7 @@
       <c r="H217" t="n">
         <v>2007</v>
       </c>
-      <c r="I217" s="2" t="n">
-        <v>46934</v>
-      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="J217" t="n">
         <v>110000</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>47299</v>
       </c>
       <c r="J219" t="n">
-        <v>465000</v>
+        <v>930000</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -10384,7 +10384,9 @@
       <c r="H220" t="n">
         <v>2006</v>
       </c>
-      <c r="I220" t="inlineStr"/>
+      <c r="I220" s="2" t="n">
+        <v>47664</v>
+      </c>
       <c r="J220" t="n">
         <v>110000</v>
       </c>
@@ -10610,10 +10612,10 @@
         <v>2004</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="J225" t="n">
-        <v>1000000</v>
+        <v>2100000</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -11429,7 +11431,7 @@
         <v>47848</v>
       </c>
       <c r="J243" t="n">
-        <v>540000</v>
+        <v>750000</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -11540,7 +11542,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>GY-M-S Megye I. osztály</t>
+          <t>Gy-M-S Vármegyei I. osztály</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11832,7 +11834,7 @@
         <v>47299</v>
       </c>
       <c r="J252" t="n">
-        <v>520000</v>
+        <v>785000</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
@@ -12010,7 +12012,7 @@
         <v>47664</v>
       </c>
       <c r="J256" t="n">
-        <v>480000</v>
+        <v>360000</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
@@ -12153,17 +12155,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>NK Nafta Lendava 1903</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2nd SNL</t>
+          <t>NB I</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -12218,7 +12220,9 @@
           <t>Finland</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr"/>
+      <c r="F261" t="n">
+        <v>185</v>
+      </c>
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="n">
         <v>2006</v>
@@ -12509,7 +12513,7 @@
         <v>46934</v>
       </c>
       <c r="J267" t="n">
-        <v>410000</v>
+        <v>720000</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -12644,9 +12648,7 @@
       <c r="H270" t="n">
         <v>2006</v>
       </c>
-      <c r="I270" s="2" t="n">
-        <v>46752</v>
-      </c>
+      <c r="I270" t="inlineStr"/>
       <c r="J270" t="n">
         <v>545000</v>
       </c>
@@ -13495,7 +13497,7 @@
         <v>2007</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="J290" t="n">
         <v>580000</v>
@@ -13776,12 +13778,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Flora Tallinn U21</t>
+          <t>Flora Tallinn</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Esiliiga</t>
+          <t>Premium Liiga</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -13841,7 +13843,7 @@
         <v>2005</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>46752</v>
+        <v>47483</v>
       </c>
       <c r="J298" t="n">
         <v>365000</v>
@@ -13905,12 +13907,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Hammarby Talang FF</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Ettan, Norra</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14163,8 +14165,14 @@
       <c r="I306" s="2" t="n">
         <v>47118</v>
       </c>
-      <c r="J306" t="inlineStr"/>
-      <c r="K306" t="inlineStr"/>
+      <c r="J306" t="n">
+        <v>185000</v>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -14531,7 +14539,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>No team</t>
+          <t>AF Elbasani</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -14965,19 +14973,11 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Parva Liga</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
+          <t>No team</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
           <t>Bulgaria</t>
@@ -15209,11 +15209,19 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PFC CSKA II Sofia</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Bulgarian Cup</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>Bulgaria</t>
@@ -16418,17 +16426,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>HNK Rijeka U19</t>
+          <t>HNK Rijeka</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Kvarnerska Rivijera</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>World</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -16465,12 +16473,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>HNK Rijeka</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>3. HNL, East</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -16553,17 +16561,17 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>NK Lokomotiva Zagreb</t>
+          <t>SK Brann</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>Eliteserien</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -16571,13 +16579,19 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
+      <c r="F362" t="n">
+        <v>185</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H362" t="n">
         <v>2005</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>47299</v>
+        <v>47483</v>
       </c>
       <c r="J362" t="n">
         <v>1000000</v>
@@ -16999,8 +17013,14 @@
       <c r="I372" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr"/>
+      <c r="J372" t="n">
+        <v>23000</v>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -17178,7 +17198,9 @@
       <c r="H376" t="n">
         <v>2005</v>
       </c>
-      <c r="I376" t="inlineStr"/>
+      <c r="I376" s="2" t="n">
+        <v>46387</v>
+      </c>
       <c r="J376" t="n">
         <v>260000</v>
       </c>
@@ -19502,7 +19524,7 @@
         <v>46203</v>
       </c>
       <c r="J428" t="n">
-        <v>755000</v>
+        <v>945000</v>
       </c>
       <c r="K428" t="inlineStr">
         <is>
@@ -19548,8 +19570,14 @@
       <c r="I429" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="J429" t="inlineStr"/>
-      <c r="K429" t="inlineStr"/>
+      <c r="J429" t="n">
+        <v>205000</v>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -21462,7 +21490,7 @@
       </c>
       <c r="I472" t="inlineStr"/>
       <c r="J472" t="n">
-        <v>970000</v>
+        <v>1500000</v>
       </c>
       <c r="K472" t="inlineStr">
         <is>
@@ -21476,12 +21504,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>FK RFS II</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Virsliga</t>
+          <t>1.Division</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -21491,17 +21519,29 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="F473" t="inlineStr"/>
-      <c r="G473" t="inlineStr"/>
+          <t>Congo Republic</t>
+        </is>
+      </c>
+      <c r="F473" t="n">
+        <v>182</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H473" t="n">
         <v>2005</v>
       </c>
       <c r="I473" t="inlineStr"/>
-      <c r="J473" t="inlineStr"/>
-      <c r="K473" t="inlineStr"/>
+      <c r="J473" t="n">
+        <v>215000</v>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -21902,7 +21942,7 @@
         <v>47299</v>
       </c>
       <c r="J482" t="n">
-        <v>47000</v>
+        <v>140000</v>
       </c>
       <c r="K482" t="inlineStr">
         <is>
@@ -22380,12 +22420,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Kuopion Palloseura</t>
+          <t>KuPS Akatemia</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Veikkausliiga</t>
+          <t>Kakkonen, Group A</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -22896,9 +22936,7 @@
       <c r="H504" t="n">
         <v>2005</v>
       </c>
-      <c r="I504" s="2" t="n">
-        <v>46934</v>
-      </c>
+      <c r="I504" t="inlineStr"/>
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr"/>
     </row>

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -8356,9 +8356,7 @@
       <c r="H176" t="n">
         <v>2004</v>
       </c>
-      <c r="I176" s="2" t="n">
-        <v>47664</v>
-      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="J176" t="n">
         <v>730000</v>
       </c>
@@ -10140,12 +10138,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Veikkausliiga</t>
+          <t>Ykkosliiga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -18173,12 +18171,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>Young Violets Austria Wien</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>2. Liga</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K507"/>
+  <dimension ref="A1:K509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,9 +1088,7 @@
       <c r="H14" t="n">
         <v>2005</v>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>46568</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>580000</v>
       </c>
@@ -11288,9 +11286,7 @@
       <c r="H240" t="n">
         <v>2006</v>
       </c>
-      <c r="I240" s="2" t="n">
-        <v>47299</v>
-      </c>
+      <c r="I240" t="inlineStr"/>
       <c r="J240" t="n">
         <v>515000</v>
       </c>
@@ -13412,9 +13408,7 @@
       <c r="H288" t="n">
         <v>2006</v>
       </c>
-      <c r="I288" s="2" t="n">
-        <v>47118</v>
-      </c>
+      <c r="I288" t="inlineStr"/>
       <c r="J288" t="n">
         <v>740000</v>
       </c>
@@ -18171,12 +18165,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Young Violets Austria Wien</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2. Liga</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -20737,9 +20731,7 @@
       <c r="H455" t="n">
         <v>2007</v>
       </c>
-      <c r="I455" s="2" t="n">
-        <v>46356</v>
-      </c>
+      <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr"/>
     </row>
@@ -21621,9 +21613,7 @@
       <c r="H475" t="n">
         <v>2006</v>
       </c>
-      <c r="I475" s="2" t="n">
-        <v>46934</v>
-      </c>
+      <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr"/>
     </row>
@@ -22973,9 +22963,7 @@
       <c r="H505" t="n">
         <v>2004</v>
       </c>
-      <c r="I505" s="2" t="n">
-        <v>46934</v>
-      </c>
+      <c r="I505" t="inlineStr"/>
       <c r="J505" t="n">
         <v>440000</v>
       </c>
@@ -23070,6 +23058,94 @@
       <c r="I507" t="inlineStr"/>
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>660</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>HJK</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr"/>
+      <c r="H508" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I508" s="2" t="n">
+        <v>46752</v>
+      </c>
+      <c r="J508" t="n">
+        <v>47000</v>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>661</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>HJK</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F509" t="n">
+        <v>187</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H509" t="n">
+        <v>2006</v>
+      </c>
+      <c r="I509" s="2" t="n">
+        <v>46387</v>
+      </c>
+      <c r="J509" t="n">
+        <v>96000</v>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -2082,12 +2082,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VVV-Venlo</t>
+          <t>Jong VVV-Venlo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eerste Divisie</t>
+          <t>Reservecompetitie, 2nd Stage, Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4879,7 +4879,7 @@
         <v>47118</v>
       </c>
       <c r="J99" t="n">
-        <v>110000</v>
+        <v>54000</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>47664</v>
       </c>
       <c r="J109" t="n">
-        <v>315000</v>
+        <v>525000</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>47299</v>
       </c>
       <c r="J121" t="n">
-        <v>775000</v>
+        <v>875000</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Utsiktens BK</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Superettan</t>
+          <t>Ettan, Sodra</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6360,7 +6360,7 @@
         <v>2006</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
@@ -7986,7 +7986,7 @@
         <v>47664</v>
       </c>
       <c r="J168" t="n">
-        <v>780000</v>
+        <v>625000</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>2005</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>46203</v>
+        <v>46568</v>
       </c>
       <c r="J182" t="n">
         <v>660000</v>
@@ -8914,7 +8914,9 @@
       <c r="H188" t="n">
         <v>2007</v>
       </c>
-      <c r="I188" t="inlineStr"/>
+      <c r="I188" s="2" t="n">
+        <v>47299</v>
+      </c>
       <c r="J188" t="n">
         <v>1500000</v>
       </c>
@@ -9276,7 +9278,11 @@
       <c r="F196" t="n">
         <v>186</v>
       </c>
-      <c r="G196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H196" t="n">
         <v>2005</v>
       </c>
@@ -9284,7 +9290,7 @@
         <v>46568</v>
       </c>
       <c r="J196" t="n">
-        <v>230000</v>
+        <v>185000</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -12642,7 +12648,9 @@
       <c r="H270" t="n">
         <v>2006</v>
       </c>
-      <c r="I270" t="inlineStr"/>
+      <c r="I270" s="2" t="n">
+        <v>46752</v>
+      </c>
       <c r="J270" t="n">
         <v>545000</v>
       </c>
@@ -12803,10 +12811,10 @@
         <v>2006</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="J274" t="n">
-        <v>230000</v>
+        <v>320000</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -12978,7 +12986,7 @@
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="n">
-        <v>120000</v>
+        <v>140000</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -13408,9 +13416,11 @@
       <c r="H288" t="n">
         <v>2006</v>
       </c>
-      <c r="I288" t="inlineStr"/>
+      <c r="I288" s="2" t="n">
+        <v>47118</v>
+      </c>
       <c r="J288" t="n">
-        <v>740000</v>
+        <v>2600000</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
@@ -13483,8 +13493,14 @@
           <t>Norway</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
+      <c r="F290" t="n">
+        <v>186</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H290" t="n">
         <v>2007</v>
       </c>
@@ -16418,17 +16434,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>HNK Rijeka</t>
+          <t>HNK Rijeka U19</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>Kvarnerska Rivijera</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>World</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -19747,9 +19763,7 @@
       <c r="H433" t="n">
         <v>2007</v>
       </c>
-      <c r="I433" s="2" t="n">
-        <v>47118</v>
-      </c>
+      <c r="I433" t="inlineStr"/>
       <c r="J433" t="n">
         <v>365000</v>
       </c>
@@ -21742,7 +21756,7 @@
         <v>47118</v>
       </c>
       <c r="J478" t="n">
-        <v>110000</v>
+        <v>430000</v>
       </c>
       <c r="K478" t="inlineStr">
         <is>
@@ -22568,7 +22582,7 @@
         <v>46203</v>
       </c>
       <c r="J496" t="n">
-        <v>485000</v>
+        <v>1900000</v>
       </c>
       <c r="K496" t="inlineStr">
         <is>

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NK Lokomotiva Zagreb</t>
+          <t>NK Hrvatski Dragovoljac</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Liga III Seria 10</t>
+          <t>Superscore Liga 3 Seria 10</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -14486,7 +14486,7 @@
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -18181,12 +18181,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>Young Violets Austria Wien</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>2. Liga</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Liga III Seria 9</t>
+          <t>Superscore Liga 3 Seria 9</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -21981,7 +21981,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H483" t="n">

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K515"/>
+  <dimension ref="A1:K521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,7 +1088,9 @@
       <c r="H14" t="n">
         <v>2005</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" s="2" t="n">
+        <v>46568</v>
+      </c>
       <c r="J14" t="n">
         <v>580000</v>
       </c>
@@ -1317,7 +1319,7 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>825000</v>
+        <v>775000</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1483,7 +1485,9 @@
       <c r="H23" t="n">
         <v>2005</v>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" s="2" t="n">
+        <v>47664</v>
+      </c>
       <c r="J23" t="n">
         <v>1600000</v>
       </c>
@@ -1940,8 +1944,14 @@
         <v>2005</v>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>115000</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2121,12 +2131,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VVV-Venlo</t>
+          <t>Jong VVV-Venlo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eerste Divisie</t>
+          <t>Reservecompetitie, 2nd Stage, Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2528,19 +2538,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sandefjord Fotball II</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>3rd Division, Group 3</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
+          <t>No team</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Bosnia &amp;amp; Herzegovina</t>
@@ -2626,7 +2628,9 @@
           <t>Norway</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>190</v>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Right</t>
@@ -3045,7 +3049,7 @@
         <v>2005</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46387</v>
+        <v>46201</v>
       </c>
       <c r="J58" t="n">
         <v>48000</v>
@@ -3095,7 +3099,7 @@
         <v>46203</v>
       </c>
       <c r="J59" t="n">
-        <v>230000</v>
+        <v>275000</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3310,7 +3314,7 @@
         <v>46568</v>
       </c>
       <c r="J64" t="n">
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3357,7 +3361,7 @@
         <v>46934</v>
       </c>
       <c r="J65" t="n">
-        <v>340000</v>
+        <v>290000</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3588,7 +3592,7 @@
         <v>47664</v>
       </c>
       <c r="J70" t="n">
-        <v>325000</v>
+        <v>420000</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3635,7 +3639,7 @@
         <v>47299</v>
       </c>
       <c r="J71" t="n">
-        <v>395000</v>
+        <v>345000</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -4703,9 +4707,11 @@
       <c r="H95" t="n">
         <v>2005</v>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" s="2" t="n">
+        <v>47664</v>
+      </c>
       <c r="J95" t="n">
-        <v>5300000</v>
+        <v>4300000</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -4932,7 +4938,7 @@
         <v>46568</v>
       </c>
       <c r="J100" t="n">
-        <v>415000</v>
+        <v>645000</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -5418,7 +5424,7 @@
         <v>2006</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="J111" t="n">
         <v>475000</v>
@@ -5513,7 +5519,7 @@
         <v>47299</v>
       </c>
       <c r="J113" t="n">
-        <v>515000</v>
+        <v>825000</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -5601,7 +5607,7 @@
         <v>47848</v>
       </c>
       <c r="J115" t="n">
-        <v>1000000</v>
+        <v>1200000</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -5615,12 +5621,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Hammarby Talang FF</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ettan, Norra</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6109,9 +6115,11 @@
       <c r="H127" t="n">
         <v>2006</v>
       </c>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" s="2" t="n">
+        <v>46752</v>
+      </c>
       <c r="J127" t="n">
-        <v>210000</v>
+        <v>315000</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -6273,7 +6281,9 @@
       <c r="H131" t="n">
         <v>2006</v>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" s="2" t="n">
+        <v>47664</v>
+      </c>
       <c r="J131" t="n">
         <v>47000</v>
       </c>
@@ -6598,7 +6608,7 @@
         <v>47299</v>
       </c>
       <c r="J138" t="n">
-        <v>1200000</v>
+        <v>1100000</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -6688,7 +6698,9 @@
       <c r="H140" t="n">
         <v>2004</v>
       </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" s="2" t="n">
+        <v>46387</v>
+      </c>
       <c r="J140" t="n">
         <v>195000</v>
       </c>
@@ -7440,7 +7452,7 @@
         <v>47299</v>
       </c>
       <c r="J156" t="n">
-        <v>430000</v>
+        <v>380000</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -7628,7 +7640,7 @@
         <v>46568</v>
       </c>
       <c r="J160" t="n">
-        <v>970000</v>
+        <v>1100000</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -7720,7 +7732,7 @@
         <v>47299</v>
       </c>
       <c r="J162" t="n">
-        <v>775000</v>
+        <v>670000</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -7900,7 +7912,9 @@
       <c r="H166" t="n">
         <v>2005</v>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" s="2" t="n">
+        <v>47483</v>
+      </c>
       <c r="J166" t="n">
         <v>1100000</v>
       </c>
@@ -8272,7 +8286,7 @@
         <v>46904</v>
       </c>
       <c r="J174" t="n">
-        <v>950000</v>
+        <v>1400000</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -8360,7 +8374,9 @@
       <c r="H176" t="n">
         <v>2004</v>
       </c>
-      <c r="I176" t="inlineStr"/>
+      <c r="I176" s="2" t="n">
+        <v>47664</v>
+      </c>
       <c r="J176" t="n">
         <v>730000</v>
       </c>
@@ -8499,7 +8515,9 @@
       <c r="H179" t="n">
         <v>2004</v>
       </c>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" s="2" t="n">
+        <v>47299</v>
+      </c>
       <c r="J179" t="n">
         <v>1300000</v>
       </c>
@@ -9108,7 +9126,9 @@
       <c r="H192" t="n">
         <v>2004</v>
       </c>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" s="2" t="n">
+        <v>46203</v>
+      </c>
       <c r="J192" t="n">
         <v>205000</v>
       </c>
@@ -9142,7 +9162,9 @@
           <t>Gambia</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
+      <c r="F193" t="n">
+        <v>180</v>
+      </c>
       <c r="G193" t="inlineStr">
         <is>
           <t>Left</t>
@@ -9625,7 +9647,7 @@
         <v>47299</v>
       </c>
       <c r="J203" t="n">
-        <v>655000</v>
+        <v>710000</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -9719,7 +9741,7 @@
         <v>47299</v>
       </c>
       <c r="J205" t="n">
-        <v>260000</v>
+        <v>340000</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -10060,12 +10082,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Kakkonen, Group C</t>
+          <t>Veikkausliiga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10078,8 +10100,14 @@
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
+      <c r="F213" t="n">
+        <v>195</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H213" t="n">
         <v>2006</v>
       </c>
@@ -10148,12 +10176,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Ykkosliiga</t>
+          <t>Veikkausliiga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10169,7 +10197,11 @@
       <c r="F215" t="n">
         <v>170</v>
       </c>
-      <c r="G215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H215" t="n">
         <v>2008</v>
       </c>
@@ -10209,7 +10241,9 @@
           <t>Georgia</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
+      <c r="F216" t="n">
+        <v>180</v>
+      </c>
       <c r="G216" t="inlineStr">
         <is>
           <t>Right</t>
@@ -10261,7 +10295,9 @@
       <c r="H217" t="n">
         <v>2007</v>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" s="2" t="n">
+        <v>46934</v>
+      </c>
       <c r="J217" t="n">
         <v>110000</v>
       </c>
@@ -10482,7 +10518,7 @@
         <v>46568</v>
       </c>
       <c r="J222" t="n">
-        <v>205000</v>
+        <v>515000</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -10746,7 +10782,11 @@
       <c r="F228" t="n">
         <v>186</v>
       </c>
-      <c r="G228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="H228" t="n">
         <v>2004</v>
       </c>
@@ -11063,7 +11103,11 @@
       <c r="F235" t="n">
         <v>181</v>
       </c>
-      <c r="G235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H235" t="n">
         <v>2005</v>
       </c>
@@ -11247,7 +11291,11 @@
       <c r="F239" t="n">
         <v>180</v>
       </c>
-      <c r="G239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H239" t="n">
         <v>2005</v>
       </c>
@@ -11298,7 +11346,9 @@
       <c r="H240" t="n">
         <v>2006</v>
       </c>
-      <c r="I240" t="inlineStr"/>
+      <c r="I240" s="2" t="n">
+        <v>47299</v>
+      </c>
       <c r="J240" t="n">
         <v>515000</v>
       </c>
@@ -11382,7 +11432,11 @@
       <c r="F242" t="n">
         <v>180</v>
       </c>
-      <c r="G242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H242" t="n">
         <v>2006</v>
       </c>
@@ -11616,8 +11670,14 @@
       <c r="I247" s="2" t="n">
         <v>47848</v>
       </c>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
+      <c r="J247" t="n">
+        <v>185000</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -11658,7 +11718,7 @@
         <v>46752</v>
       </c>
       <c r="J248" t="n">
-        <v>465000</v>
+        <v>655000</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
@@ -12053,7 +12113,11 @@
       <c r="F257" t="n">
         <v>182</v>
       </c>
-      <c r="G257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H257" t="n">
         <v>2004</v>
       </c>
@@ -12161,17 +12225,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>NK Nafta Lendava 1903</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>NB I</t>
+          <t>2nd SNL</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -12229,7 +12293,11 @@
       <c r="F261" t="n">
         <v>185</v>
       </c>
-      <c r="G261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H261" t="n">
         <v>2006</v>
       </c>
@@ -12699,7 +12767,7 @@
         <v>47483</v>
       </c>
       <c r="J271" t="n">
-        <v>210000</v>
+        <v>180000</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -13072,13 +13140,17 @@
       <c r="F280" t="n">
         <v>169</v>
       </c>
-      <c r="G280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H280" t="n">
         <v>2006</v>
       </c>
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="n">
-        <v>290000</v>
+        <v>390000</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -13472,8 +13544,14 @@
       <c r="I289" s="2" t="n">
         <v>46752</v>
       </c>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
+      <c r="J289" t="n">
+        <v>79000</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -13601,8 +13679,14 @@
       <c r="I292" s="2" t="n">
         <v>46387</v>
       </c>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
+      <c r="J292" t="n">
+        <v>46000</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -13642,8 +13726,14 @@
       <c r="I293" s="2" t="n">
         <v>47118</v>
       </c>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
+      <c r="J293" t="n">
+        <v>45000</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -13684,7 +13774,7 @@
         <v>46934</v>
       </c>
       <c r="J294" t="n">
-        <v>750000</v>
+        <v>940000</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -13731,7 +13821,7 @@
         <v>47118</v>
       </c>
       <c r="J295" t="n">
-        <v>27000</v>
+        <v>54000</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -13778,7 +13868,7 @@
         <v>46934</v>
       </c>
       <c r="J296" t="n">
-        <v>935000</v>
+        <v>1400000</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -13792,12 +13882,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Flora Tallinn</t>
+          <t>Flora Tallinn U21</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Premium Liiga</t>
+          <t>Esiliiga</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -13811,7 +13901,11 @@
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H297" t="n">
         <v>2008</v>
       </c>
@@ -13921,12 +14015,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Hammarby Talang FF</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Ettan, Norra</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -13945,7 +14039,7 @@
         <v>2008</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>46356</v>
+        <v>46752</v>
       </c>
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr"/>
@@ -14138,8 +14232,14 @@
       <c r="I305" s="2" t="n">
         <v>47483</v>
       </c>
-      <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr"/>
+      <c r="J305" t="n">
+        <v>120000</v>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -14532,8 +14632,14 @@
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr"/>
-      <c r="G315" t="inlineStr"/>
+      <c r="F315" t="n">
+        <v>180</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
       <c r="H315" t="n">
         <v>2007</v>
       </c>
@@ -14611,11 +14717,17 @@
       <c r="F317" t="n">
         <v>187</v>
       </c>
-      <c r="G317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H317" t="n">
         <v>2006</v>
       </c>
-      <c r="I317" t="inlineStr"/>
+      <c r="I317" s="2" t="n">
+        <v>46387</v>
+      </c>
       <c r="J317" t="n">
         <v>205000</v>
       </c>
@@ -14660,7 +14772,7 @@
       </c>
       <c r="I318" t="inlineStr"/>
       <c r="J318" t="n">
-        <v>320000</v>
+        <v>270000</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
@@ -15223,19 +15335,11 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Bulgarian Cup</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
+          <t>PFC CSKA II Sofia</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>Bulgaria</t>
@@ -15486,8 +15590,14 @@
       <c r="I337" s="2" t="n">
         <v>47664</v>
       </c>
-      <c r="J337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
+      <c r="J337" t="n">
+        <v>190000</v>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -16064,7 +16174,7 @@
       </c>
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="n">
-        <v>190000</v>
+        <v>135000</v>
       </c>
       <c r="K350" t="inlineStr">
         <is>
@@ -16231,7 +16341,9 @@
           <t>Georgia</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr"/>
+      <c r="F354" t="n">
+        <v>175</v>
+      </c>
       <c r="G354" t="inlineStr">
         <is>
           <t>Left</t>
@@ -16487,12 +16599,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>HNK Rijeka</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>3. HNL, East</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -17254,7 +17366,9 @@
           <t>Norway</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr"/>
+      <c r="F377" t="n">
+        <v>183</v>
+      </c>
       <c r="G377" t="inlineStr">
         <is>
           <t>Left</t>
@@ -17266,8 +17380,14 @@
       <c r="I377" s="2" t="n">
         <v>46387</v>
       </c>
-      <c r="J377" t="inlineStr"/>
-      <c r="K377" t="inlineStr"/>
+      <c r="J377" t="n">
+        <v>195000</v>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -17352,7 +17472,7 @@
         <v>2006</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="J379" t="n">
         <v>620000</v>
@@ -17670,7 +17790,11 @@
       <c r="F386" t="n">
         <v>190</v>
       </c>
-      <c r="G386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H386" t="n">
         <v>2007</v>
       </c>
@@ -17940,7 +18064,11 @@
       <c r="F392" t="n">
         <v>188</v>
       </c>
-      <c r="G392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H392" t="n">
         <v>2007</v>
       </c>
@@ -18193,12 +18321,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Young Violets Austria Wien</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2. Liga</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -18582,7 +18710,7 @@
         <v>47299</v>
       </c>
       <c r="J406" t="n">
-        <v>430000</v>
+        <v>1100000</v>
       </c>
       <c r="K406" t="inlineStr">
         <is>
@@ -18949,7 +19077,7 @@
         <v>46934</v>
       </c>
       <c r="J415" t="n">
-        <v>155000</v>
+        <v>180000</v>
       </c>
       <c r="K415" t="inlineStr">
         <is>
@@ -19497,7 +19625,7 @@
         <v>46568</v>
       </c>
       <c r="J427" t="n">
-        <v>1100000</v>
+        <v>3200000</v>
       </c>
       <c r="K427" t="inlineStr">
         <is>
@@ -19685,7 +19813,7 @@
         <v>46387</v>
       </c>
       <c r="J431" t="n">
-        <v>160000</v>
+        <v>215000</v>
       </c>
       <c r="K431" t="inlineStr">
         <is>
@@ -19775,9 +19903,11 @@
       <c r="H433" t="n">
         <v>2007</v>
       </c>
-      <c r="I433" t="inlineStr"/>
+      <c r="I433" s="2" t="n">
+        <v>47118</v>
+      </c>
       <c r="J433" t="n">
-        <v>365000</v>
+        <v>455000</v>
       </c>
       <c r="K433" t="inlineStr">
         <is>
@@ -20151,7 +20281,7 @@
         <v>47483</v>
       </c>
       <c r="J441" t="n">
-        <v>680000</v>
+        <v>775000</v>
       </c>
       <c r="K441" t="inlineStr">
         <is>
@@ -20198,7 +20328,7 @@
         <v>46568</v>
       </c>
       <c r="J442" t="n">
-        <v>370000</v>
+        <v>470000</v>
       </c>
       <c r="K442" t="inlineStr">
         <is>
@@ -20245,7 +20375,7 @@
         <v>47483</v>
       </c>
       <c r="J443" t="n">
-        <v>235000</v>
+        <v>255000</v>
       </c>
       <c r="K443" t="inlineStr">
         <is>
@@ -20468,7 +20598,7 @@
       </c>
       <c r="I448" t="inlineStr"/>
       <c r="J448" t="n">
-        <v>285000</v>
+        <v>570000</v>
       </c>
       <c r="K448" t="inlineStr">
         <is>
@@ -20535,8 +20665,14 @@
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
+      <c r="F450" t="n">
+        <v>181</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H450" t="n">
         <v>2006</v>
       </c>
@@ -20589,7 +20725,7 @@
         <v>46203</v>
       </c>
       <c r="J451" t="n">
-        <v>260000</v>
+        <v>465000</v>
       </c>
       <c r="K451" t="inlineStr">
         <is>
@@ -20636,7 +20772,7 @@
         <v>46568</v>
       </c>
       <c r="J452" t="n">
-        <v>670000</v>
+        <v>960000</v>
       </c>
       <c r="K452" t="inlineStr">
         <is>
@@ -20757,7 +20893,9 @@
       <c r="H455" t="n">
         <v>2007</v>
       </c>
-      <c r="I455" t="inlineStr"/>
+      <c r="I455" s="2" t="n">
+        <v>46356</v>
+      </c>
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr"/>
     </row>
@@ -21017,7 +21155,11 @@
       <c r="F461" t="n">
         <v>185</v>
       </c>
-      <c r="G461" t="inlineStr"/>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H461" t="n">
         <v>2006</v>
       </c>
@@ -21149,7 +21291,7 @@
         <v>2008</v>
       </c>
       <c r="I464" s="2" t="n">
-        <v>46387</v>
+        <v>47073</v>
       </c>
       <c r="J464" t="n">
         <v>79000</v>
@@ -21375,7 +21517,7 @@
         <v>46203</v>
       </c>
       <c r="J469" t="n">
-        <v>285000</v>
+        <v>360000</v>
       </c>
       <c r="K469" t="inlineStr">
         <is>
@@ -21596,7 +21738,7 @@
         <v>46934</v>
       </c>
       <c r="J474" t="n">
-        <v>570000</v>
+        <v>715000</v>
       </c>
       <c r="K474" t="inlineStr">
         <is>
@@ -21639,9 +21781,17 @@
       <c r="H475" t="n">
         <v>2006</v>
       </c>
-      <c r="I475" t="inlineStr"/>
-      <c r="J475" t="inlineStr"/>
-      <c r="K475" t="inlineStr"/>
+      <c r="I475" s="2" t="n">
+        <v>46934</v>
+      </c>
+      <c r="J475" t="n">
+        <v>480000</v>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -21725,7 +21875,7 @@
         <v>47299</v>
       </c>
       <c r="J477" t="n">
-        <v>215000</v>
+        <v>320000</v>
       </c>
       <c r="K477" t="inlineStr">
         <is>
@@ -22097,7 +22247,7 @@
         <v>46934</v>
       </c>
       <c r="J485" t="n">
-        <v>260000</v>
+        <v>360000</v>
       </c>
       <c r="K485" t="inlineStr">
         <is>
@@ -22270,7 +22420,9 @@
           <t>Mali</t>
         </is>
       </c>
-      <c r="F489" t="inlineStr"/>
+      <c r="F489" t="n">
+        <v>178</v>
+      </c>
       <c r="G489" t="inlineStr">
         <is>
           <t>Right</t>
@@ -22412,7 +22564,11 @@
       <c r="F492" t="n">
         <v>178</v>
       </c>
-      <c r="G492" t="inlineStr"/>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H492" t="n">
         <v>2005</v>
       </c>
@@ -22434,12 +22590,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>KuPS Akatemia</t>
+          <t>Kuopion Palloseura</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Kakkonen, Group A</t>
+          <t>Veikkausliiga</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -22729,7 +22885,7 @@
         <v>46203</v>
       </c>
       <c r="J499" t="n">
-        <v>79000</v>
+        <v>130000</v>
       </c>
       <c r="K499" t="inlineStr">
         <is>
@@ -22950,7 +23106,9 @@
       <c r="H504" t="n">
         <v>2005</v>
       </c>
-      <c r="I504" t="inlineStr"/>
+      <c r="I504" s="2" t="n">
+        <v>46934</v>
+      </c>
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr"/>
     </row>
@@ -22989,7 +23147,9 @@
       <c r="H505" t="n">
         <v>2004</v>
       </c>
-      <c r="I505" t="inlineStr"/>
+      <c r="I505" s="2" t="n">
+        <v>46934</v>
+      </c>
       <c r="J505" t="n">
         <v>440000</v>
       </c>
@@ -23109,8 +23269,14 @@
           <t>Finland</t>
         </is>
       </c>
-      <c r="F508" t="inlineStr"/>
-      <c r="G508" t="inlineStr"/>
+      <c r="F508" t="n">
+        <v>179</v>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
       <c r="H508" t="n">
         <v>2007</v>
       </c>
@@ -23250,8 +23416,14 @@
         <v>2007</v>
       </c>
       <c r="I511" t="inlineStr"/>
-      <c r="J511" t="inlineStr"/>
-      <c r="K511" t="inlineStr"/>
+      <c r="J511" t="n">
+        <v>97000</v>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -23424,6 +23596,272 @@
         <v>27000</v>
       </c>
       <c r="K515" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>668</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>NŠ Mura</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>PrvaLiga</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H516" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I516" s="2" t="n">
+        <v>46934</v>
+      </c>
+      <c r="J516" t="n">
+        <v>97000</v>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>669</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>FC Košice</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2. Liga</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="F517" t="n">
+        <v>170</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="H517" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I517" s="2" t="n">
+        <v>47269</v>
+      </c>
+      <c r="J517" t="n">
+        <v>260000</v>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>670</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>SC Austria Lustenau</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2. Liga</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F518" t="n">
+        <v>179</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H518" t="n">
+        <v>2006</v>
+      </c>
+      <c r="I518" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="J518" t="n">
+        <v>265000</v>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>671</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Rapid Wien II</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2. Liga</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="F519" t="n">
+        <v>171</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H519" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I519" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="J519" t="n">
+        <v>270000</v>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>672</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>HB Køge</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Betinia Liga</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr"/>
+      <c r="H520" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I520" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="J520" t="n">
+        <v>370000</v>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>673</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>ETO Akadémia</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Gy-M-S Vármegyei I. osztály</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Hungary Amateur</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Gambia</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr"/>
+      <c r="H521" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="n">
+        <v>97000</v>
+      </c>
+      <c r="K521" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -14659,11 +14659,19 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>AF Elbasani</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr"/>
-      <c r="D316" t="inlineStr"/>
+          <t>New York Red Bulls II</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>USL Championship</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>Nigeria</t>

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K521"/>
+  <dimension ref="A1:K527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16290,12 +16290,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>FC Torpedo Kutaisi</t>
+          <t>Torpedo Kutaisi U19</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Erovnuli Liga</t>
+          <t>U19 Soccer League</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -23875,6 +23875,250 @@
         </is>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>674</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Moss FK</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2nd Division, Group 1</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="F522" t="n">
+        <v>183</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="H522" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I522" s="2" t="n">
+        <v>46387</v>
+      </c>
+      <c r="J522" t="n">
+        <v>92000</v>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>675</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>FK Auda</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>1.Division</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="F523" t="n">
+        <v>196</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H523" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="n">
+        <v>205000</v>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>676</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Górnik Zabrze II</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>III Liga, Group 3</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H524" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="inlineStr"/>
+      <c r="K524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>677</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>CS Gloria Bistrița</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr"/>
+      <c r="D525" t="inlineStr"/>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="H525" t="n">
+        <v>2004</v>
+      </c>
+      <c r="I525" t="inlineStr"/>
+      <c r="J525" t="n">
+        <v>72000</v>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>678</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>FC Corvinul Hunedoara</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Superscore Liga 3 Seria 9</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="F526" t="n">
+        <v>181</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="H526" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I526" t="inlineStr"/>
+      <c r="J526" t="n">
+        <v>70000</v>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>679</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>AC Horsens</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Betinia Liga</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr"/>
+      <c r="H527" t="n">
+        <v>2008</v>
+      </c>
+      <c r="I527" s="2" t="n">
+        <v>47299</v>
+      </c>
+      <c r="J527" t="inlineStr"/>
+      <c r="K527" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -904,7 +904,7 @@
         <v>46203</v>
       </c>
       <c r="J10" t="n">
-        <v>190000</v>
+        <v>165000</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>115000</v>
+        <v>160000</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FK Crvena zvezda</t>
+          <t>FK Napredak Kruševac</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Hammarby IF</t>
+          <t>Hammarby Talang FF</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Ettan, Norra</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
-        <v>1100000</v>
+        <v>845000</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>2004</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>46568</v>
+        <v>46203</v>
       </c>
       <c r="J178" t="n">
         <v>475000</v>
@@ -10270,12 +10270,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>FC Ajka</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>NB I</t>
+          <t>NB II</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -11732,17 +11732,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>NK Osijek U19</t>
+          <t>NK Osijek</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Kvarnerska Rivijera</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>World</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -12026,8 +12026,14 @@
           <t>Kosovo</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
+      <c r="F255" t="n">
+        <v>181</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="H255" t="n">
         <v>2008</v>
       </c>
@@ -14688,7 +14694,9 @@
       <c r="H316" t="n">
         <v>2006</v>
       </c>
-      <c r="I316" t="inlineStr"/>
+      <c r="I316" s="2" t="n">
+        <v>46387</v>
+      </c>
       <c r="J316" t="n">
         <v>160000</v>
       </c>
@@ -19162,7 +19170,9 @@
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr"/>
+      <c r="F417" t="n">
+        <v>178</v>
+      </c>
       <c r="G417" t="inlineStr">
         <is>
           <t>Right</t>
@@ -20684,7 +20694,9 @@
       <c r="H450" t="n">
         <v>2006</v>
       </c>
-      <c r="I450" t="inlineStr"/>
+      <c r="I450" s="2" t="n">
+        <v>47664</v>
+      </c>
       <c r="J450" t="n">
         <v>485000</v>
       </c>
@@ -21609,7 +21621,9 @@
       <c r="H471" t="n">
         <v>2006</v>
       </c>
-      <c r="I471" t="inlineStr"/>
+      <c r="I471" s="2" t="n">
+        <v>46934</v>
+      </c>
       <c r="J471" t="n">
         <v>27000</v>
       </c>
@@ -22128,12 +22142,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>FC Liefering</t>
+          <t>Red Bull Salzburg</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2. Liga</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K527"/>
+  <dimension ref="A1:K528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Mjøndalen IF</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -14021,12 +14021,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Hammarby Talang FF</t>
+          <t>Hammarby IF</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Ettan, Norra</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -15312,11 +15312,19 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PFC CSKA II Sofia</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Bulgarian Cup</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>Bulgaria</t>
@@ -21639,19 +21647,11 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>FK Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>Mozzart Bet Prva Liga</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>Serbia</t>
-        </is>
-      </c>
+          <t>No team</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr"/>
+      <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
           <t>Serbia</t>
@@ -24133,6 +24133,47 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr"/>
     </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>680</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Turun Palloseura</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F528" t="n">
+        <v>184</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="H528" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I528" s="2" t="n">
+        <v>46387</v>
+      </c>
+      <c r="J528" t="inlineStr"/>
+      <c r="K528" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/players_profiles.xlsx
+++ b/players_profiles.xlsx
@@ -572,10 +572,10 @@
         <v>2005</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46203</v>
+        <v>46568</v>
       </c>
       <c r="J3" t="n">
-        <v>340000</v>
+        <v>390000</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         <v>46934</v>
       </c>
       <c r="J4" t="n">
-        <v>485000</v>
+        <v>580000</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>46568</v>
       </c>
       <c r="J12" t="n">
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1185,8 +1185,14 @@
       <c r="I16" s="2" t="n">
         <v>46752</v>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>275000</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1489,7 +1495,7 @@
         <v>47664</v>
       </c>
       <c r="J23" t="n">
-        <v>1600000</v>
+        <v>2100000</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2084,7 +2090,7 @@
         <v>47118</v>
       </c>
       <c r="J36" t="n">
-        <v>1400000</v>
+        <v>2500000</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2197,7 +2203,7 @@
         <v>46568</v>
       </c>
       <c r="J39" t="n">
-        <v>290000</v>
+        <v>220000</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2244,7 +2250,7 @@
         <v>47118</v>
       </c>
       <c r="J40" t="n">
-        <v>470000</v>
+        <v>940000</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2291,7 +2297,7 @@
         <v>46752</v>
       </c>
       <c r="J41" t="n">
-        <v>330000</v>
+        <v>280000</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2524,7 +2530,7 @@
         <v>46234</v>
       </c>
       <c r="J46" t="n">
-        <v>290000</v>
+        <v>335000</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2596,7 +2602,7 @@
         <v>46752</v>
       </c>
       <c r="J48" t="n">
-        <v>620000</v>
+        <v>515000</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2643,7 +2649,7 @@
         <v>47330</v>
       </c>
       <c r="J49" t="n">
-        <v>420000</v>
+        <v>525000</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2782,7 +2788,7 @@
         <v>47118</v>
       </c>
       <c r="J52" t="n">
-        <v>660000</v>
+        <v>750000</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3422,12 +3428,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CSM Olimpia Satu Mare</t>
+          <t>Chindia Târgoviște</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Superscore Liga 3 Seria 10</t>
+          <t>Superliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3731,7 +3737,7 @@
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
-        <v>340000</v>
+        <v>440000</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -3821,7 +3827,7 @@
         <v>46568</v>
       </c>
       <c r="J75" t="n">
-        <v>180000</v>
+        <v>230000</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -3962,7 +3968,7 @@
         <v>46538</v>
       </c>
       <c r="J78" t="n">
-        <v>110000</v>
+        <v>440000</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4267,7 +4273,7 @@
         <v>46203</v>
       </c>
       <c r="J85" t="n">
-        <v>52000</v>
+        <v>105000</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4353,9 +4359,7 @@
       <c r="H87" t="n">
         <v>2004</v>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>46173</v>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
         <v>380000</v>
       </c>
@@ -4402,7 +4406,7 @@
         <v>46203</v>
       </c>
       <c r="J88" t="n">
-        <v>105000</v>
+        <v>205000</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4592,11 +4596,19 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SU Dinamo Jug Vranje</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
+          <t>FK Vojvodina</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Mozzart Bet Superliga</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>Serbia</t>
@@ -4772,12 +4784,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Famalicão U23</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Liga Portugal Betclic</t>
+          <t>U23 Championship, 1st Phase, North</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4866,11 +4878,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Crown Legacy FC</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+          <t>FK Čukarički</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Mozzart Bet Superliga</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>Serbia</t>
@@ -5953,7 +5973,7 @@
         <v>47118</v>
       </c>
       <c r="J123" t="n">
-        <v>2000000</v>
+        <v>1600000</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -6346,12 +6366,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Utsiktens BK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ettan, Sodra</t>
+          <t>Superettan</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6984,7 +7004,7 @@
         <v>47299</v>
       </c>
       <c r="J146" t="n">
-        <v>280000</v>
+        <v>235000</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -7125,7 +7145,7 @@
         <v>46934</v>
       </c>
       <c r="J149" t="n">
-        <v>660000</v>
+        <v>570000</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -7170,7 +7190,7 @@
         <v>46934</v>
       </c>
       <c r="J150" t="n">
-        <v>580000</v>
+        <v>680000</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -7264,7 +7284,7 @@
         <v>46568</v>
       </c>
       <c r="J152" t="n">
-        <v>315000</v>
+        <v>290000</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -7466,17 +7486,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ETO Akadémia</t>
+          <t>ETO FC Győr</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Gy-M-S Vármegyei I. osztály</t>
+          <t>NB II</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Hungary Amateur</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7916,7 +7936,7 @@
         <v>47483</v>
       </c>
       <c r="J166" t="n">
-        <v>1100000</v>
+        <v>2700000</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -8472,7 +8492,7 @@
         <v>46203</v>
       </c>
       <c r="J178" t="n">
-        <v>475000</v>
+        <v>525000</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -8660,7 +8680,7 @@
         <v>46568</v>
       </c>
       <c r="J182" t="n">
-        <v>660000</v>
+        <v>770000</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -8707,7 +8727,7 @@
         <v>47848</v>
       </c>
       <c r="J183" t="n">
-        <v>1500000</v>
+        <v>1700000</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -8848,7 +8868,7 @@
         <v>47664</v>
       </c>
       <c r="J186" t="n">
-        <v>370000</v>
+        <v>275000</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -8942,7 +8962,7 @@
         <v>47299</v>
       </c>
       <c r="J188" t="n">
-        <v>1500000</v>
+        <v>2600000</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -9083,7 +9103,7 @@
         <v>46203</v>
       </c>
       <c r="J191" t="n">
-        <v>660000</v>
+        <v>570000</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -9459,7 +9479,7 @@
         <v>47269</v>
       </c>
       <c r="J199" t="n">
-        <v>620000</v>
+        <v>825000</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -9647,7 +9667,7 @@
         <v>47299</v>
       </c>
       <c r="J203" t="n">
-        <v>710000</v>
+        <v>765000</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -9741,7 +9761,7 @@
         <v>47299</v>
       </c>
       <c r="J205" t="n">
-        <v>340000</v>
+        <v>260000</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -10700,7 +10720,7 @@
         <v>47848</v>
       </c>
       <c r="J226" t="n">
-        <v>845000</v>
+        <v>635000</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
@@ -11209,7 +11229,7 @@
         <v>47299</v>
       </c>
       <c r="J237" t="n">
-        <v>465000</v>
+        <v>560000</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
@@ -11597,17 +11617,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ETO Akadémia</t>
+          <t>ETO FC Győr</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Gy-M-S Vármegyei I. osztály</t>
+          <t>NB II</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Hungary Amateur</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -11765,7 +11785,7 @@
         <v>46568</v>
       </c>
       <c r="J249" t="n">
-        <v>46000</v>
+        <v>185000</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
@@ -11994,7 +12014,7 @@
         <v>47299</v>
       </c>
       <c r="J254" t="n">
-        <v>280000</v>
+        <v>470000</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -12178,7 +12198,7 @@
         <v>47118</v>
       </c>
       <c r="J258" t="n">
-        <v>245000</v>
+        <v>290000</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
@@ -13066,7 +13086,7 @@
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="n">
-        <v>140000</v>
+        <v>165000</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -13598,7 +13618,7 @@
         <v>47483</v>
       </c>
       <c r="J290" t="n">
-        <v>580000</v>
+        <v>970000</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -13960,7 +13980,7 @@
         <v>47483</v>
       </c>
       <c r="J298" t="n">
-        <v>365000</v>
+        <v>550000</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
@@ -14333,7 +14353,7 @@
         <v>47299</v>
       </c>
       <c r="J307" t="n">
-        <v>775000</v>
+        <v>1200000</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
@@ -14882,7 +14902,7 @@
         <v>46904</v>
       </c>
       <c r="J320" t="n">
-        <v>190000</v>
+        <v>240000</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
@@ -14929,7 +14949,7 @@
         <v>46385</v>
       </c>
       <c r="J321" t="n">
-        <v>290000</v>
+        <v>485000</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
@@ -15135,7 +15155,7 @@
         <v>2008</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>46568</v>
+        <v>47664</v>
       </c>
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr"/>
@@ -15312,19 +15332,11 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Bulgarian Cup</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
+          <t>PFC CSKA II Sofia</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
           <t>Bulgaria</t>
@@ -15345,7 +15357,7 @@
         <v>46934</v>
       </c>
       <c r="J331" t="n">
-        <v>53000</v>
+        <v>105000</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
@@ -15384,7 +15396,7 @@
         <v>46203</v>
       </c>
       <c r="J332" t="n">
-        <v>160000</v>
+        <v>215000</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
@@ -16024,7 +16036,7 @@
         <v>46934</v>
       </c>
       <c r="J346" t="n">
-        <v>660000</v>
+        <v>880000</v>
       </c>
       <c r="K346" t="inlineStr">
         <is>
@@ -16114,7 +16126,7 @@
         <v>46568</v>
       </c>
       <c r="J348" t="n">
-        <v>380000</v>
+        <v>520000</v>
       </c>
       <c r="K348" t="inlineStr">
         <is>
@@ -16245,7 +16257,7 @@
         <v>46203</v>
       </c>
       <c r="J351" t="n">
-        <v>320000</v>
+        <v>215000</v>
       </c>
       <c r="K351" t="inlineStr">
         <is>
@@ -16576,17 +16588,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>HNK Rijeka U19</t>
+          <t>HNK Rijeka</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Kvarnerska Rivijera</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>World</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -16791,7 +16803,7 @@
         <v>46934</v>
       </c>
       <c r="J363" t="n">
-        <v>320000</v>
+        <v>770000</v>
       </c>
       <c r="K363" t="inlineStr">
         <is>
@@ -16930,7 +16942,7 @@
         <v>47299</v>
       </c>
       <c r="J366" t="n">
-        <v>440000</v>
+        <v>545000</v>
       </c>
       <c r="K366" t="inlineStr">
         <is>
@@ -16971,7 +16983,7 @@
         <v>46203</v>
       </c>
       <c r="J367" t="n">
-        <v>440000</v>
+        <v>485000</v>
       </c>
       <c r="K367" t="inlineStr">
         <is>
@@ -17311,7 +17323,7 @@
         <v>47118</v>
       </c>
       <c r="J375" t="n">
-        <v>555000</v>
+        <v>650000</v>
       </c>
       <c r="K375" t="inlineStr">
         <is>
@@ -17640,7 +17652,7 @@
         <v>46387</v>
       </c>
       <c r="J382" t="n">
-        <v>365000</v>
+        <v>340000</v>
       </c>
       <c r="K382" t="inlineStr">
         <is>
@@ -17734,7 +17746,7 @@
         <v>46387</v>
       </c>
       <c r="J384" t="n">
-        <v>180000</v>
+        <v>270000</v>
       </c>
       <c r="K384" t="inlineStr">
         <is>
@@ -17779,7 +17791,7 @@
       </c>
       <c r="I385" t="inlineStr"/>
       <c r="J385" t="n">
-        <v>155000</v>
+        <v>515000</v>
       </c>
       <c r="K385" t="inlineStr">
         <is>
@@ -18331,7 +18343,7 @@
         <v>47664</v>
       </c>
       <c r="J397" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="K397" t="inlineStr">
         <is>
@@ -19240,7 +19252,7 @@
         <v>46387</v>
       </c>
       <c r="J418" t="n">
-        <v>195000</v>
+        <v>97000</v>
       </c>
       <c r="K418" t="inlineStr">
         <is>
@@ -19281,9 +19293,7 @@
       <c r="H419" t="n">
         <v>2007</v>
       </c>
-      <c r="I419" s="2" t="n">
-        <v>46173</v>
-      </c>
+      <c r="I419" t="inlineStr"/>
       <c r="J419" t="n">
         <v>215000</v>
       </c>
@@ -19424,7 +19434,7 @@
         <v>46904</v>
       </c>
       <c r="J422" t="n">
-        <v>155000</v>
+        <v>105000</v>
       </c>
       <c r="K422" t="inlineStr">
         <is>
@@ -20841,7 +20851,7 @@
       </c>
       <c r="I453" t="inlineStr"/>
       <c r="J453" t="n">
-        <v>165000</v>
+        <v>110000</v>
       </c>
       <c r="K453" t="inlineStr">
         <is>
@@ -21148,7 +21158,7 @@
         <v>46934</v>
       </c>
       <c r="J460" t="n">
-        <v>710000</v>
+        <v>1100000</v>
       </c>
       <c r="K460" t="inlineStr">
         <is>
@@ -21192,7 +21202,7 @@
         <v>2006</v>
       </c>
       <c r="I461" s="2" t="n">
-        <v>46387</v>
+        <v>47118</v>
       </c>
       <c r="J461" t="n">
         <v>155000</v>
@@ -21257,7 +21267,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>1 deild</t>
+          <t>Iceland 1. deild</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -21296,7 +21306,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>1 deild</t>
+          <t>Iceland 1. deild</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -21545,7 +21555,7 @@
         <v>46203</v>
       </c>
       <c r="J469" t="n">
-        <v>360000</v>
+        <v>620000</v>
       </c>
       <c r="K469" t="inlineStr">
         <is>
@@ -21647,11 +21657,19 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>No team</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
+          <t>FK Javor Ivanjica</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Mozzart Bet Prva Liga</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>Serbia</t>
@@ -21940,7 +21958,7 @@
         <v>47118</v>
       </c>
       <c r="J478" t="n">
-        <v>430000</v>
+        <v>540000</v>
       </c>
       <c r="K478" t="inlineStr">
         <is>
@@ -22410,7 +22428,7 @@
         <v>46203</v>
       </c>
       <c r="J488" t="n">
-        <v>325000</v>
+        <v>220000</v>
       </c>
       <c r="K488" t="inlineStr">
         <is>
@@ -22504,7 +22522,7 @@
         <v>47269</v>
       </c>
       <c r="J490" t="n">
-        <v>620000</v>
+        <v>825000</v>
       </c>
       <c r="K490" t="inlineStr">
         <is>
@@ -22860,7 +22878,7 @@
         <v>47483</v>
       </c>
       <c r="J498" t="n">
-        <v>620000</v>
+        <v>3100000</v>
       </c>
       <c r="K498" t="inlineStr">
         <is>
@@ -23044,7 +23062,7 @@
         <v>47664</v>
       </c>
       <c r="J502" t="n">
-        <v>260000</v>
+        <v>410000</v>
       </c>
       <c r="K502" t="inlineStr">
         <is>
@@ -23234,17 +23252,17 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>FK Borac Banja Luka U19</t>
+          <t>FK Borac Banja Luka</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Club Friendly Games</t>
+          <t>Cup</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>World</t>
+          <t>Bosnia &amp;amp; Herzegovina</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -23707,7 +23725,7 @@
         <v>47269</v>
       </c>
       <c r="J517" t="n">
-        <v>260000</v>
+        <v>415000</v>
       </c>
       <c r="K517" t="inlineStr">
         <is>
@@ -23842,7 +23860,7 @@
         <v>46568</v>
       </c>
       <c r="J520" t="n">
-        <v>370000</v>
+        <v>630000</v>
       </c>
       <c r="K520" t="inlineStr">
         <is>
@@ -23856,17 +23874,17 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>ETO Akadémia</t>
+          <t>ETO FC Győr</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Gy-M-S Vármegyei I. osztály</t>
+          <t>NB II</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Hungary Amateur</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -24024,11 +24042,19 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>CS Gloria Bistrița</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr"/>
-      <c r="D525" t="inlineStr"/>
+          <t>CFR 1907 Cluj</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Superliga</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
       <c r="E525" t="inlineStr">
         <is>
           <t>Ghana</t>
